--- a/exports/trend_1d/CUMMINSIND_full_report.xlsx
+++ b/exports/trend_1d/CUMMINSIND_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q67"/>
+  <dimension ref="A1:U67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>10.18</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42086</v>
+        <v>42087</v>
       </c>
       <c r="H2" t="n">
-        <v>869.65</v>
+        <v>856.85</v>
       </c>
       <c r="I2" t="n">
         <v>859.4001546684376</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K2" t="n">
-        <v>-2.04</v>
+        <v>-3.49</v>
       </c>
       <c r="L2" t="n">
-        <v>3.07</v>
+        <v>5.22</v>
       </c>
       <c r="M2" t="n">
         <v>0.38</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>8.09</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42152</v>
+        <v>42153</v>
       </c>
       <c r="H3" t="n">
-        <v>850.25</v>
+        <v>918.35</v>
       </c>
       <c r="I3" t="n">
         <v>892.8288499527542</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K3" t="n">
-        <v>0.77</v>
+        <v>-7.18</v>
       </c>
       <c r="L3" t="n">
-        <v>5.15</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="M3" t="n">
         <v>1.56</v>
       </c>
       <c r="N3" t="n">
-        <v>2.81</v>
+        <v>8.01</v>
       </c>
       <c r="O3" t="n">
         <v>-1.47</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>4</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>10.39</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42237</v>
+        <v>42240</v>
       </c>
       <c r="H4" t="n">
-        <v>1141.9</v>
+        <v>1041.59</v>
       </c>
       <c r="I4" t="n">
         <v>1057.733530069479</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="K4" t="n">
-        <v>24.34</v>
+        <v>13.42</v>
       </c>
       <c r="L4" t="n">
         <v>11.05</v>
@@ -669,7 +716,7 @@
         <v>7.81</v>
       </c>
       <c r="N4" t="n">
-        <v>3.07</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="O4" t="n">
         <v>8.01</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>19.76</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42552</v>
+        <v>42555</v>
       </c>
       <c r="H5" t="n">
-        <v>843.85</v>
+        <v>852.5</v>
       </c>
       <c r="I5" t="n">
         <v>849.2390349968323</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="K5" t="n">
-        <v>18.98</v>
+        <v>18.15</v>
       </c>
       <c r="L5" t="n">
         <v>12.19</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>211</v>
+        <v>212</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>12</v>
+      </c>
+      <c r="U5" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>7.57</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42584</v>
+        <v>42585</v>
       </c>
       <c r="H6" t="n">
-        <v>850.65</v>
+        <v>826.3</v>
       </c>
       <c r="I6" t="n">
         <v>839.6782795308749</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.22</v>
+        <v>-3.07</v>
       </c>
       <c r="L6" t="n">
-        <v>4.63</v>
+        <v>4.99</v>
       </c>
       <c r="M6" t="n">
         <v>0.64</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42579</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>9.529999999999999</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42611</v>
+        <v>42612</v>
       </c>
       <c r="H7" t="n">
-        <v>900.5</v>
+        <v>917.2</v>
       </c>
       <c r="I7" t="n">
         <v>905.0150121555491</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K7" t="n">
-        <v>-8.98</v>
+        <v>-11</v>
       </c>
       <c r="L7" t="n">
-        <v>12.43</v>
+        <v>12.79</v>
       </c>
       <c r="M7" t="n">
         <v>1.15</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42607</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>7.86</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42656</v>
+        <v>42657</v>
       </c>
       <c r="H8" t="n">
-        <v>875.4</v>
+        <v>869.7</v>
       </c>
       <c r="I8" t="n">
         <v>871.5698152772416</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K8" t="n">
-        <v>-4.56</v>
+        <v>-5.18</v>
       </c>
       <c r="L8" t="n">
-        <v>4.74</v>
+        <v>5.57</v>
       </c>
       <c r="M8" t="n">
         <v>0.74</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42642</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>7.72</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42737</v>
+        <v>42738</v>
       </c>
       <c r="H9" t="n">
-        <v>826.15</v>
+        <v>842.9</v>
       </c>
       <c r="I9" t="n">
         <v>842.4832045234181</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K9" t="n">
-        <v>5.01</v>
+        <v>3.08</v>
       </c>
       <c r="L9" t="n">
         <v>3.6</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42670</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>7.66</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42874</v>
+        <v>42877</v>
       </c>
       <c r="H10" t="n">
-        <v>972.95</v>
+        <v>930.8</v>
       </c>
       <c r="I10" t="n">
         <v>966.1410553111667</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="K10" t="n">
-        <v>15.43</v>
+        <v>10.43</v>
       </c>
       <c r="L10" t="n">
         <v>5.79</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>93</v>
+        <v>94</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>5</v>
+      </c>
+      <c r="U10" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>17.33</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42935</v>
+        <v>42936</v>
       </c>
       <c r="H11" t="n">
-        <v>966.4</v>
+        <v>974.45</v>
       </c>
       <c r="I11" t="n">
         <v>968.5811286996232</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K11" t="n">
-        <v>-3.82</v>
+        <v>-4.69</v>
       </c>
       <c r="L11" t="n">
         <v>5.29</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>6.92</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42950</v>
+        <v>42951</v>
       </c>
       <c r="H12" t="n">
-        <v>949.3</v>
+        <v>936.6</v>
       </c>
       <c r="I12" t="n">
         <v>942.528622034568</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.58</v>
+        <v>-3.88</v>
       </c>
       <c r="L12" t="n">
-        <v>4</v>
+        <v>6.51</v>
       </c>
       <c r="M12" t="n">
         <v>0.89</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42943</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>9.880000000000001</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>43091</v>
+        <v>43095</v>
       </c>
       <c r="H13" t="n">
-        <v>877.15</v>
+        <v>925.65</v>
       </c>
       <c r="I13" t="n">
         <v>891.9169559420072</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="K13" t="n">
-        <v>6.35</v>
+        <v>1.17</v>
       </c>
       <c r="L13" t="n">
         <v>1.86</v>
@@ -1182,7 +1337,7 @@
         <v>2.02</v>
       </c>
       <c r="N13" t="n">
-        <v>3.86</v>
+        <v>5.53</v>
       </c>
       <c r="O13" t="n">
         <v>-1.34</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>96</v>
+        <v>97</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>5</v>
+      </c>
+      <c r="U13" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -1218,28 +1385,28 @@
         <v>8.84</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>43132</v>
+        <v>43133</v>
       </c>
       <c r="H14" t="n">
-        <v>903.05</v>
+        <v>829.2</v>
       </c>
       <c r="I14" t="n">
         <v>884.6647354845443</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.44</v>
+        <v>-10.42</v>
       </c>
       <c r="L14" t="n">
-        <v>4.94</v>
+        <v>13.67</v>
       </c>
       <c r="M14" t="n">
-        <v>0.53</v>
+        <v>1.54</v>
       </c>
       <c r="N14" t="n">
-        <v>2.84</v>
+        <v>8.18</v>
       </c>
       <c r="O14" t="n">
         <v>5.53</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>12.96</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>43229</v>
+        <v>43230</v>
       </c>
       <c r="H15" t="n">
-        <v>775.25</v>
+        <v>778.15</v>
       </c>
       <c r="I15" t="n">
         <v>776.0129177978105</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K15" t="n">
-        <v>6.51</v>
+        <v>6.16</v>
       </c>
       <c r="L15" t="n">
         <v>7.23</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>4</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -1332,25 +1523,25 @@
         <v>10.22</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43244</v>
+        <v>43245</v>
       </c>
       <c r="H16" t="n">
-        <v>719.85</v>
+        <v>701.8</v>
       </c>
       <c r="I16" t="n">
         <v>702.5998383812874</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K16" t="n">
-        <v>-7.49</v>
+        <v>-9.81</v>
       </c>
       <c r="L16" t="n">
-        <v>8.76</v>
+        <v>10.52</v>
       </c>
       <c r="M16" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="N16" t="n">
         <v>3.45</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>10.63</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43307</v>
+        <v>43308</v>
       </c>
       <c r="H17" t="n">
-        <v>675.75</v>
+        <v>679.6</v>
       </c>
       <c r="I17" t="n">
         <v>677.7245804251646</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K17" t="n">
-        <v>3.71</v>
+        <v>3.16</v>
       </c>
       <c r="L17" t="n">
         <v>3.59</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>4</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>8.859999999999999</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43362</v>
+        <v>43364</v>
       </c>
       <c r="H18" t="n">
-        <v>723.15</v>
+        <v>684.65</v>
       </c>
       <c r="I18" t="n">
         <v>703.5896210974209</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K18" t="n">
-        <v>6.41</v>
+        <v>0.74</v>
       </c>
       <c r="L18" t="n">
         <v>5.08</v>
@@ -1467,7 +1682,7 @@
         <v>0.93</v>
       </c>
       <c r="N18" t="n">
-        <v>3.96</v>
+        <v>5.32</v>
       </c>
       <c r="O18" t="n">
         <v>0.57</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>15.1</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43403</v>
+        <v>43404</v>
       </c>
       <c r="H19" t="n">
-        <v>673.3</v>
+        <v>746.85</v>
       </c>
       <c r="I19" t="n">
         <v>727.1282726345322</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K19" t="n">
-        <v>1.66</v>
+        <v>-9.08</v>
       </c>
       <c r="L19" t="n">
-        <v>6.76</v>
+        <v>12.38</v>
       </c>
       <c r="M19" t="n">
-        <v>1.07</v>
+        <v>8.42</v>
       </c>
       <c r="N19" t="n">
-        <v>4.26</v>
+        <v>10.92</v>
       </c>
       <c r="O19" t="n">
         <v>-5.32</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>13.01</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43493</v>
+        <v>43494</v>
       </c>
       <c r="H20" t="n">
-        <v>809.05</v>
+        <v>784.95</v>
       </c>
       <c r="I20" t="n">
         <v>797.4197943524318</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K20" t="n">
-        <v>8.33</v>
+        <v>5.1</v>
       </c>
       <c r="L20" t="n">
         <v>2.26</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>10.97</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43532</v>
+        <v>43535</v>
       </c>
       <c r="H21" t="n">
-        <v>730.4</v>
+        <v>748.8</v>
       </c>
       <c r="I21" t="n">
         <v>745.5954815589243</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K21" t="n">
-        <v>6.95</v>
+        <v>4.61</v>
       </c>
       <c r="L21" t="n">
         <v>3.96</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,22 +1937,22 @@
         <v>11.22</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43595</v>
+        <v>43598</v>
       </c>
       <c r="H22" t="n">
-        <v>699.85</v>
+        <v>691.15</v>
       </c>
       <c r="I22" t="n">
         <v>695.7555207350688</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K22" t="n">
-        <v>-6.54</v>
+        <v>-7.7</v>
       </c>
       <c r="L22" t="n">
-        <v>7.08</v>
+        <v>8.42</v>
       </c>
       <c r="M22" t="n">
         <v>0.82</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>8.44</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43602</v>
+        <v>43605</v>
       </c>
       <c r="H23" t="n">
-        <v>709.85</v>
+        <v>766.05</v>
       </c>
       <c r="I23" t="n">
         <v>749.4830414754451</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.71</v>
+        <v>-10.84</v>
       </c>
       <c r="L23" t="n">
-        <v>3.28</v>
+        <v>11.55</v>
       </c>
       <c r="M23" t="n">
-        <v>0.58</v>
+        <v>1.43</v>
       </c>
       <c r="N23" t="n">
-        <v>1.87</v>
+        <v>7.92</v>
       </c>
       <c r="O23" t="n">
         <v>-1.24</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>11.57</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43675</v>
+        <v>43676</v>
       </c>
       <c r="H24" t="n">
-        <v>723.85</v>
+        <v>702.05</v>
       </c>
       <c r="I24" t="n">
         <v>714.8104955824215</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K24" t="n">
-        <v>-5.51</v>
+        <v>-8.35</v>
       </c>
       <c r="L24" t="n">
-        <v>7.19</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="M24" t="n">
         <v>1.6</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>4</v>
+      </c>
+      <c r="U24" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1845,25 +2144,25 @@
         <v>11.6</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43728</v>
+        <v>43731</v>
       </c>
       <c r="H25" t="n">
-        <v>596.35</v>
+        <v>624.05</v>
       </c>
       <c r="I25" t="n">
         <v>617.8277264878724</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K25" t="n">
-        <v>15.06</v>
+        <v>11.11</v>
       </c>
       <c r="L25" t="n">
         <v>3.72</v>
       </c>
       <c r="M25" t="n">
-        <v>1.55</v>
+        <v>2.95</v>
       </c>
       <c r="N25" t="n">
         <v>4.95</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>11.01</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43741</v>
+        <v>43742</v>
       </c>
       <c r="H26" t="n">
-        <v>559.5</v>
+        <v>550.8</v>
       </c>
       <c r="I26" t="n">
         <v>555.3545415448233</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K26" t="n">
-        <v>-10.34</v>
+        <v>-11.74</v>
       </c>
       <c r="L26" t="n">
-        <v>10.86</v>
+        <v>13.74</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>12.66</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43815</v>
+        <v>43816</v>
       </c>
       <c r="H27" t="n">
-        <v>545.95</v>
+        <v>562.05</v>
       </c>
       <c r="I27" t="n">
         <v>559.9602343051458</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K27" t="n">
-        <v>0.88</v>
+        <v>-2.04</v>
       </c>
       <c r="L27" t="n">
         <v>8.01</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>10.15</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43868</v>
+        <v>43871</v>
       </c>
       <c r="H28" t="n">
-        <v>558.05</v>
+        <v>546.7</v>
       </c>
       <c r="I28" t="n">
         <v>554.1713206095988</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.71</v>
+        <v>-2.73</v>
       </c>
       <c r="L28" t="n">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="M28" t="n">
         <v>1.19</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43825</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>11.8</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43936</v>
+        <v>43937</v>
       </c>
       <c r="H29" t="n">
-        <v>375.4</v>
+        <v>389.8</v>
       </c>
       <c r="I29" t="n">
         <v>385.4185053710394</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K29" t="n">
-        <v>31.33</v>
+        <v>28.7</v>
       </c>
       <c r="L29" t="n">
         <v>2.71</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>26.73</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43966</v>
+        <v>43969</v>
       </c>
       <c r="H30" t="n">
-        <v>338.35</v>
+        <v>317.5</v>
       </c>
       <c r="I30" t="n">
         <v>337.2366114293575</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K30" t="n">
-        <v>-13.2</v>
+        <v>-18.55</v>
       </c>
       <c r="L30" t="n">
-        <v>14.06</v>
+        <v>20.16</v>
       </c>
       <c r="M30" t="n">
         <v>5.17</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,25 +2558,25 @@
         <v>23.24</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43987</v>
+        <v>43990</v>
       </c>
       <c r="H31" t="n">
-        <v>384.35</v>
+        <v>399.2</v>
       </c>
       <c r="I31" t="n">
         <v>388.6574219670598</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K31" t="n">
-        <v>-21.06</v>
+        <v>-25.73</v>
       </c>
       <c r="L31" t="n">
-        <v>24.6</v>
+        <v>27.15</v>
       </c>
       <c r="M31" t="n">
-        <v>1.42</v>
+        <v>2.51</v>
       </c>
       <c r="N31" t="n">
         <v>4.63</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43979</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>14.08</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44026</v>
+        <v>44027</v>
       </c>
       <c r="H32" t="n">
-        <v>386.65</v>
+        <v>380.25</v>
       </c>
       <c r="I32" t="n">
         <v>382.6449979940909</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K32" t="n">
-        <v>-3.14</v>
+        <v>-4.75</v>
       </c>
       <c r="L32" t="n">
         <v>7.73</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>13.51</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44055</v>
+        <v>44056</v>
       </c>
       <c r="H33" t="n">
-        <v>423.05</v>
+        <v>436.75</v>
       </c>
       <c r="I33" t="n">
         <v>424.3857584039201</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K33" t="n">
-        <v>-11.26</v>
+        <v>-14.86</v>
       </c>
       <c r="L33" t="n">
-        <v>12.58</v>
+        <v>18</v>
       </c>
       <c r="M33" t="n">
         <v>1</v>
       </c>
       <c r="N33" t="n">
-        <v>2.16</v>
+        <v>3.24</v>
       </c>
       <c r="O33" t="n">
         <v>-1.66</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44042</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>10.46</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44112</v>
+        <v>44113</v>
       </c>
       <c r="H34" t="n">
-        <v>446.95</v>
+        <v>432.1</v>
       </c>
       <c r="I34" t="n">
         <v>433.443857439494</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K34" t="n">
-        <v>2.34</v>
+        <v>-1.06</v>
       </c>
       <c r="L34" t="n">
         <v>5.3</v>
@@ -2379,7 +2786,7 @@
         <v>1.57</v>
       </c>
       <c r="N34" t="n">
-        <v>2.99</v>
+        <v>3.32</v>
       </c>
       <c r="O34" t="n">
         <v>3.24</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44070</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>13.22</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44146</v>
+        <v>44147</v>
       </c>
       <c r="H35" t="n">
-        <v>456.55</v>
+        <v>478.55</v>
       </c>
       <c r="I35" t="n">
         <v>478.3187025403957</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K35" t="n">
-        <v>-5.66</v>
+        <v>-10.75</v>
       </c>
       <c r="L35" t="n">
-        <v>10.16</v>
+        <v>11.63</v>
       </c>
       <c r="M35" t="n">
         <v>0.88</v>
       </c>
       <c r="N35" t="n">
-        <v>4.3</v>
+        <v>4.82</v>
       </c>
       <c r="O35" t="n">
         <v>-3.32</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>11.26</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44342</v>
+        <v>44343</v>
       </c>
       <c r="H36" t="n">
-        <v>802.65</v>
+        <v>771.75</v>
       </c>
       <c r="I36" t="n">
         <v>796.5563132075409</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K36" t="n">
-        <v>67.73</v>
+        <v>61.27</v>
       </c>
       <c r="L36" t="n">
         <v>4.69</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>131</v>
+        <v>132</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>7</v>
+      </c>
+      <c r="U36" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>13.7</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44376</v>
+        <v>44377</v>
       </c>
       <c r="H37" t="n">
-        <v>850.95</v>
+        <v>899.5</v>
       </c>
       <c r="I37" t="n">
         <v>877.0292023769179</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K37" t="n">
-        <v>-10.26</v>
+        <v>-16.55</v>
       </c>
       <c r="L37" t="n">
-        <v>13.93</v>
+        <v>17.25</v>
       </c>
       <c r="M37" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="N37" t="n">
-        <v>3.14</v>
+        <v>5.71</v>
       </c>
       <c r="O37" t="n">
         <v>-3.85</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44371</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>10.68</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44469</v>
+        <v>44470</v>
       </c>
       <c r="H38" t="n">
-        <v>991.95</v>
+        <v>918.1</v>
       </c>
       <c r="I38" t="n">
         <v>966.7161074178503</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K38" t="n">
-        <v>10.28</v>
+        <v>2.07</v>
       </c>
       <c r="L38" t="n">
         <v>8.66</v>
@@ -2607,7 +3062,7 @@
         <v>6.51</v>
       </c>
       <c r="N38" t="n">
-        <v>3.68</v>
+        <v>7.44</v>
       </c>
       <c r="O38" t="n">
         <v>5.71</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>4</v>
+      </c>
+      <c r="U38" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>15.24</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44536</v>
+        <v>44537</v>
       </c>
       <c r="H39" t="n">
-        <v>924.4</v>
+        <v>943.75</v>
       </c>
       <c r="I39" t="n">
         <v>943.5656229407132</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-2.79</v>
       </c>
       <c r="L39" t="n">
         <v>7.59</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,22 +3179,22 @@
         <v>9.18</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44547</v>
+        <v>44550</v>
       </c>
       <c r="H40" t="n">
-        <v>915.7</v>
+        <v>894.35</v>
       </c>
       <c r="I40" t="n">
         <v>908.2155121289198</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K40" t="n">
-        <v>-2.97</v>
+        <v>-5.23</v>
       </c>
       <c r="L40" t="n">
-        <v>3.15</v>
+        <v>6.92</v>
       </c>
       <c r="M40" t="n">
         <v>1.1</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>9.789999999999999</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44574</v>
+        <v>44575</v>
       </c>
       <c r="H41" t="n">
-        <v>975.45</v>
+        <v>986.85</v>
       </c>
       <c r="I41" t="n">
         <v>981.9358272429943</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K41" t="n">
-        <v>-9.07</v>
+        <v>-10.34</v>
       </c>
       <c r="L41" t="n">
-        <v>10.14</v>
+        <v>13.83</v>
       </c>
       <c r="M41" t="n">
         <v>0.9</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>7.1</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44581</v>
+        <v>44582</v>
       </c>
       <c r="H42" t="n">
-        <v>948.05</v>
+        <v>921.3</v>
       </c>
       <c r="I42" t="n">
         <v>922.0168467104768</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K42" t="n">
-        <v>-3.93</v>
+        <v>-6.64</v>
       </c>
       <c r="L42" t="n">
-        <v>4.69</v>
+        <v>7.79</v>
       </c>
       <c r="M42" t="n">
         <v>0.06</v>
       </c>
       <c r="N42" t="n">
-        <v>2.36</v>
+        <v>2.82</v>
       </c>
       <c r="O42" t="n">
         <v>1.17</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>10.31</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44628</v>
+        <v>44629</v>
       </c>
       <c r="H43" t="n">
-        <v>945.45</v>
+        <v>1000.35</v>
       </c>
       <c r="I43" t="n">
         <v>994.3049634383041</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K43" t="n">
-        <v>-2.62</v>
+        <v>-8.58</v>
       </c>
       <c r="L43" t="n">
         <v>8.869999999999999</v>
@@ -2892,7 +3407,7 @@
         <v>2.4</v>
       </c>
       <c r="N43" t="n">
-        <v>3.72</v>
+        <v>5.81</v>
       </c>
       <c r="O43" t="n">
         <v>-2.82</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>13.23</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44673</v>
+        <v>44676</v>
       </c>
       <c r="H44" t="n">
-        <v>1060.7</v>
+        <v>998.95</v>
       </c>
       <c r="I44" t="n">
         <v>1036.419784322385</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K44" t="n">
-        <v>6.03</v>
+        <v>-0.14</v>
       </c>
       <c r="L44" t="n">
         <v>5.53</v>
       </c>
       <c r="M44" t="n">
-        <v>1.29</v>
+        <v>3.37</v>
       </c>
       <c r="N44" t="n">
-        <v>2.75</v>
+        <v>5.82</v>
       </c>
       <c r="O44" t="n">
         <v>5.81</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>13.18</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44743</v>
+        <v>44746</v>
       </c>
       <c r="H45" t="n">
-        <v>1026.1</v>
+        <v>1052.15</v>
       </c>
       <c r="I45" t="n">
         <v>1044.183135666061</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K45" t="n">
-        <v>-2.72</v>
+        <v>-5.33</v>
       </c>
       <c r="L45" t="n">
-        <v>5.31</v>
+        <v>6</v>
       </c>
       <c r="M45" t="n">
         <v>2.38</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>4</v>
+      </c>
+      <c r="U45" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>8.27</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44917</v>
+        <v>44918</v>
       </c>
       <c r="H46" t="n">
-        <v>1450.15</v>
+        <v>1388.05</v>
       </c>
       <c r="I46" t="n">
         <v>1404.103901054817</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K46" t="n">
-        <v>37.83</v>
+        <v>31.93</v>
       </c>
       <c r="L46" t="n">
         <v>2.38</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>118</v>
+        <v>119</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>6</v>
+      </c>
+      <c r="U46" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>11.74</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44965</v>
+        <v>44966</v>
       </c>
       <c r="H47" t="n">
-        <v>1474.3</v>
+        <v>1578.35</v>
       </c>
       <c r="I47" t="n">
         <v>1480.351619824459</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K47" t="n">
-        <v>-6.21</v>
+        <v>-13.71</v>
       </c>
       <c r="L47" t="n">
-        <v>9.359999999999999</v>
+        <v>16.57</v>
       </c>
       <c r="M47" t="n">
-        <v>1.2</v>
+        <v>4.46</v>
       </c>
       <c r="N47" t="n">
-        <v>3.28</v>
+        <v>7.06</v>
       </c>
       <c r="O47" t="n">
         <v>-4.28</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>9.279999999999999</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45019</v>
+        <v>45021</v>
       </c>
       <c r="H48" t="n">
-        <v>1605.25</v>
+        <v>1568.55</v>
       </c>
       <c r="I48" t="n">
         <v>1580.04107749701</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K48" t="n">
-        <v>1.7</v>
+        <v>-0.62</v>
       </c>
       <c r="L48" t="n">
         <v>2.43</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>8.65</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45051</v>
+        <v>45054</v>
       </c>
       <c r="H49" t="n">
-        <v>1595.9</v>
+        <v>1618</v>
       </c>
       <c r="I49" t="n">
         <v>1611.451886665699</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K49" t="n">
-        <v>-1.74</v>
+        <v>-3.15</v>
       </c>
       <c r="L49" t="n">
-        <v>3.27</v>
+        <v>3.82</v>
       </c>
       <c r="M49" t="n">
         <v>0.95</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,25 +3869,25 @@
         <v>6.36</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45141</v>
+        <v>45142</v>
       </c>
       <c r="H50" t="n">
-        <v>1881.05</v>
+        <v>1796.1</v>
       </c>
       <c r="I50" t="n">
         <v>1845.879333318676</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K50" t="n">
-        <v>16.26</v>
+        <v>11.01</v>
       </c>
       <c r="L50" t="n">
         <v>3.83</v>
       </c>
       <c r="M50" t="n">
-        <v>1.27</v>
+        <v>1.65</v>
       </c>
       <c r="N50" t="n">
         <v>5.31</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>4</v>
+      </c>
+      <c r="U50" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>10.5</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45237</v>
+        <v>45238</v>
       </c>
       <c r="H51" t="n">
-        <v>1699.1</v>
+        <v>1767.2</v>
       </c>
       <c r="I51" t="n">
         <v>1761.933613737007</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K51" t="n">
-        <v>5.4</v>
+        <v>1.61</v>
       </c>
       <c r="L51" t="n">
         <v>6</v>
@@ -3348,7 +3959,7 @@
         <v>1.72</v>
       </c>
       <c r="N51" t="n">
-        <v>2.61</v>
+        <v>4.01</v>
       </c>
       <c r="O51" t="n">
         <v>-4.52</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>4</v>
+      </c>
+      <c r="U51" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>7.91</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="H52" t="n">
-        <v>3712.25</v>
+        <v>3245.9</v>
       </c>
       <c r="I52" t="n">
         <v>3529.122532029775</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K52" t="n">
-        <v>110.06</v>
+        <v>83.67</v>
       </c>
       <c r="L52" t="n">
         <v>4.26</v>
@@ -3405,7 +4028,7 @@
         <v>0.98</v>
       </c>
       <c r="N52" t="n">
-        <v>6.2</v>
+        <v>12.56</v>
       </c>
       <c r="O52" t="n">
         <v>4.01</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>141</v>
+        <v>142</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>8</v>
+      </c>
+      <c r="U52" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>21.95</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45463</v>
+        <v>45464</v>
       </c>
       <c r="H53" t="n">
-        <v>3857</v>
+        <v>3899.95</v>
       </c>
       <c r="I53" t="n">
         <v>3870.302486837333</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K53" t="n">
-        <v>-18.83</v>
+        <v>-20.15</v>
       </c>
       <c r="L53" t="n">
         <v>22.3</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>11.5</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45491</v>
+        <v>45492</v>
       </c>
       <c r="H54" t="n">
-        <v>3796.85</v>
+        <v>3559.45</v>
       </c>
       <c r="I54" t="n">
         <v>3668.853908768624</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K54" t="n">
-        <v>-2.64</v>
+        <v>-8.73</v>
       </c>
       <c r="L54" t="n">
-        <v>3.59</v>
+        <v>8.98</v>
       </c>
       <c r="M54" t="n">
         <v>1.07</v>
       </c>
       <c r="N54" t="n">
-        <v>3.35</v>
+        <v>6.25</v>
       </c>
       <c r="O54" t="n">
         <v>1.11</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>15.22</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45639</v>
+        <v>45642</v>
       </c>
       <c r="H55" t="n">
-        <v>3599.9</v>
+        <v>3671.4</v>
       </c>
       <c r="I55" t="n">
         <v>3653.664920159738</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="K55" t="n">
-        <v>-1.14</v>
+        <v>-3.15</v>
       </c>
       <c r="L55" t="n">
         <v>10.38</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>102</v>
+        <v>103</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>6</v>
+      </c>
+      <c r="U55" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>8.49</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45644</v>
+        <v>45645</v>
       </c>
       <c r="H56" t="n">
-        <v>3526.3</v>
+        <v>3357.65</v>
       </c>
       <c r="I56" t="n">
         <v>3359.642004302527</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K56" t="n">
-        <v>-3.95</v>
+        <v>-8.550000000000001</v>
       </c>
       <c r="L56" t="n">
-        <v>4.67</v>
+        <v>9</v>
       </c>
       <c r="M56" t="n">
-        <v>0.11</v>
+        <v>1.99</v>
       </c>
       <c r="N56" t="n">
-        <v>3.47</v>
+        <v>4.78</v>
       </c>
       <c r="O56" t="n">
         <v>1.99</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>10.98</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45737</v>
+        <v>45740</v>
       </c>
       <c r="H57" t="n">
-        <v>2937.75</v>
+        <v>3056.25</v>
       </c>
       <c r="I57" t="n">
         <v>3011.230503040924</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="K57" t="n">
-        <v>12.51</v>
+        <v>8.98</v>
       </c>
       <c r="L57" t="n">
         <v>3.64</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>4</v>
+      </c>
+      <c r="U57" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -3726,25 +4421,25 @@
         <v>11.05</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45751</v>
+        <v>45754</v>
       </c>
       <c r="H58" t="n">
-        <v>2844.95</v>
+        <v>2711.25</v>
       </c>
       <c r="I58" t="n">
         <v>2743.456035781126</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K58" t="n">
-        <v>-6.91</v>
+        <v>-11.29</v>
       </c>
       <c r="L58" t="n">
-        <v>7.34</v>
+        <v>15.58</v>
       </c>
       <c r="M58" t="n">
-        <v>1.48</v>
+        <v>9.31</v>
       </c>
       <c r="N58" t="n">
         <v>6.19</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>11.63</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45792</v>
+        <v>45793</v>
       </c>
       <c r="H59" t="n">
-        <v>2949.2</v>
+        <v>3035.6</v>
       </c>
       <c r="I59" t="n">
         <v>3026.631712181603</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K59" t="n">
-        <v>-8.779999999999999</v>
+        <v>-11.96</v>
       </c>
       <c r="L59" t="n">
-        <v>9.640000000000001</v>
+        <v>12.24</v>
       </c>
       <c r="M59" t="n">
         <v>4.5</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>11.06</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="H60" t="n">
-        <v>3926.5</v>
+        <v>3849</v>
       </c>
       <c r="I60" t="n">
         <v>3910.60233686536</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K60" t="n">
-        <v>29.35</v>
+        <v>26.8</v>
       </c>
       <c r="L60" t="n">
         <v>3.95</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>96</v>
+        <v>97</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>6</v>
+      </c>
+      <c r="U60" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>7.33</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="H61" t="n">
-        <v>4073.9</v>
+        <v>4183.2</v>
       </c>
       <c r="I61" t="n">
         <v>4131.10375001073</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K61" t="n">
-        <v>-5.84</v>
+        <v>-8.68</v>
       </c>
       <c r="L61" t="n">
-        <v>6.52</v>
+        <v>9.26</v>
       </c>
       <c r="M61" t="n">
         <v>0.59</v>
       </c>
       <c r="N61" t="n">
-        <v>2.17</v>
+        <v>2.68</v>
       </c>
       <c r="O61" t="n">
         <v>-1.97</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>7.17</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="H62" t="n">
-        <v>4309.8</v>
+        <v>4130.3</v>
       </c>
       <c r="I62" t="n">
         <v>4302.107450999627</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K62" t="n">
-        <v>3.03</v>
+        <v>-1.26</v>
       </c>
       <c r="L62" t="n">
         <v>3.06</v>
@@ -3975,7 +4718,7 @@
         <v>1.2</v>
       </c>
       <c r="N62" t="n">
-        <v>3.84</v>
+        <v>4.16</v>
       </c>
       <c r="O62" t="n">
         <v>2.68</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>4</v>
+      </c>
+      <c r="U62" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="63">
@@ -4011,28 +4766,28 @@
         <v>10.82</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="H63" t="n">
-        <v>4202.3</v>
+        <v>4391.4</v>
       </c>
       <c r="I63" t="n">
         <v>4257.456080898443</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K63" t="n">
-        <v>-1.74</v>
+        <v>-6.32</v>
       </c>
       <c r="L63" t="n">
-        <v>5.76</v>
+        <v>6.97</v>
       </c>
       <c r="M63" t="n">
         <v>2.27</v>
       </c>
       <c r="N63" t="n">
-        <v>2.44</v>
+        <v>4.5</v>
       </c>
       <c r="O63" t="n">
         <v>-4.16</v>
@@ -4041,7 +4796,19 @@
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>14.93</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="H64" t="n">
-        <v>4717.6</v>
+        <v>4505.7</v>
       </c>
       <c r="I64" t="n">
         <v>4561.143563238793</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K64" t="n">
-        <v>7.43</v>
+        <v>2.6</v>
       </c>
       <c r="L64" t="n">
         <v>8.18</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>13.25</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="H65" t="n">
-        <v>4907.4</v>
+        <v>5138.7</v>
       </c>
       <c r="I65" t="n">
         <v>5020.235373122944</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K65" t="n">
-        <v>-8.92</v>
+        <v>-14.05</v>
       </c>
       <c r="L65" t="n">
-        <v>9.1</v>
+        <v>14.41</v>
       </c>
       <c r="M65" t="n">
         <v>3.26</v>
       </c>
       <c r="N65" t="n">
-        <v>3.39</v>
+        <v>4.71</v>
       </c>
       <c r="O65" t="n">
         <v>-4.49</v>
@@ -4155,7 +4934,19 @@
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>12.35</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="H66" t="n">
-        <v>5455.5</v>
+        <v>5383</v>
       </c>
       <c r="I66" t="n">
         <v>5420.134278898271</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K66" t="n">
-        <v>6.16</v>
+        <v>4.75</v>
       </c>
       <c r="L66" t="n">
         <v>4.48</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>5</v>
+      </c>
+      <c r="U66" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="67">
@@ -4263,6 +5066,14 @@
       <c r="Q67" t="n">
         <v>63</v>
       </c>
+      <c r="R67" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9221,7 +10032,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>63.2</v>
+        <v>64.8</v>
       </c>
     </row>
     <row r="6">
@@ -9231,7 +10042,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7">
@@ -9241,7 +10052,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="8">
@@ -9251,7 +10062,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -9261,7 +10072,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10">
@@ -9271,7 +10082,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>136.6</v>
+        <v>138.6</v>
       </c>
     </row>
     <row r="11">
@@ -9281,7 +10092,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12">
@@ -9291,7 +10102,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13">
@@ -9301,7 +10112,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>30.8</v>
+        <v>27.7</v>
       </c>
     </row>
     <row r="14">
@@ -9311,7 +10122,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.95</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="15">
@@ -9321,7 +10132,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8.289999999999999</v>
+        <v>3.65</v>
       </c>
     </row>
     <row r="16">
@@ -9331,7 +10142,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.53</v>
+        <v>-4.19</v>
       </c>
     </row>
     <row r="17">
@@ -9341,7 +10152,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>110.06</v>
+        <v>83.67</v>
       </c>
     </row>
     <row r="18">
@@ -9351,7 +10162,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>44.6</v>
+        <v>33.8</v>
       </c>
     </row>
     <row r="19">
@@ -9361,7 +10172,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.83</v>
+        <v>8.49</v>
       </c>
     </row>
     <row r="20">
@@ -9371,7 +10182,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.31</v>
+        <v>7.59</v>
       </c>
     </row>
     <row r="21">
@@ -9381,7 +10192,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>24.6</v>
+        <v>27.15</v>
       </c>
     </row>
     <row r="22">
@@ -9391,7 +10202,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
     </row>
     <row r="23">
@@ -9401,7 +10212,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24">
@@ -9411,7 +10222,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.94</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="25">
@@ -9421,7 +10232,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>7.81</v>
+        <v>9.31</v>
       </c>
     </row>
     <row r="26">
@@ -9431,7 +10242,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.12</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="27">
@@ -9451,7 +10262,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>26</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29">
